--- a/artfynd/A 58919-2024 artfynd.xlsx
+++ b/artfynd/A 58919-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY116"/>
+  <dimension ref="A1:AY117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11636,7 +11636,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>115983586</v>
+        <v>115983369</v>
       </c>
       <c r="B100" t="n">
         <v>90359</v>
@@ -11676,10 +11676,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>531653</v>
+        <v>531319</v>
       </c>
       <c r="R100" t="n">
-        <v>7237498</v>
+        <v>7237804</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11706,12 +11706,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="AR100" t="inlineStr">
         <is>
-          <t>6212</t>
+          <t>5297</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -11736,7 +11736,7 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Julia Falk</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -11747,10 +11747,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>115983616</v>
+        <v>115983586</v>
       </c>
       <c r="B101" t="n">
-        <v>77450</v>
+        <v>90359</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11763,21 +11763,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228579</v>
+        <v>5432</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11787,10 +11787,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>531457</v>
+        <v>531653</v>
       </c>
       <c r="R101" t="n">
-        <v>7237480</v>
+        <v>7237498</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11817,12 +11817,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11836,7 +11836,7 @@
       </c>
       <c r="AR101" t="inlineStr">
         <is>
-          <t>5947</t>
+          <t>6212</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -11858,10 +11858,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>115983383</v>
+        <v>115983616</v>
       </c>
       <c r="B102" t="n">
-        <v>90359</v>
+        <v>77450</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11874,21 +11874,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11898,10 +11898,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>531194</v>
+        <v>531457</v>
       </c>
       <c r="R102" t="n">
-        <v>7237776</v>
+        <v>7237480</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -11928,12 +11928,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11947,7 +11947,7 @@
       </c>
       <c r="AR102" t="inlineStr">
         <is>
-          <t>5193</t>
+          <t>5947</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -11958,7 +11958,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Julia Falk</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -11969,10 +11969,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>115983394</v>
+        <v>115983383</v>
       </c>
       <c r="B103" t="n">
-        <v>78589</v>
+        <v>90359</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11985,21 +11985,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>864</v>
+        <v>5432</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12009,10 +12009,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>531178</v>
+        <v>531194</v>
       </c>
       <c r="R103" t="n">
-        <v>7237757</v>
+        <v>7237776</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12039,12 +12039,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="AR103" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -12069,7 +12069,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -12080,10 +12080,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>115983505</v>
+        <v>115983394</v>
       </c>
       <c r="B104" t="n">
-        <v>82248</v>
+        <v>78589</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12096,21 +12096,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12120,10 +12120,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>531002</v>
+        <v>531178</v>
       </c>
       <c r="R104" t="n">
-        <v>7237563</v>
+        <v>7237757</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12150,12 +12150,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="AR104" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -12180,7 +12180,7 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -12191,7 +12191,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>115983525</v>
+        <v>115983505</v>
       </c>
       <c r="B105" t="n">
         <v>82248</v>
@@ -12231,10 +12231,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>530980</v>
+        <v>531002</v>
       </c>
       <c r="R105" t="n">
-        <v>7237552</v>
+        <v>7237563</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -12280,7 +12280,7 @@
       </c>
       <c r="AR105" t="inlineStr">
         <is>
-          <t>5082</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -12302,10 +12302,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>115983458</v>
+        <v>115983525</v>
       </c>
       <c r="B106" t="n">
-        <v>90694</v>
+        <v>82248</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12314,25 +12314,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1506</v>
+        <v>1312</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12342,10 +12342,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>531634</v>
+        <v>530980</v>
       </c>
       <c r="R106" t="n">
-        <v>7237587</v>
+        <v>7237552</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -12372,12 +12372,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12391,7 +12391,7 @@
       </c>
       <c r="AR106" t="inlineStr">
         <is>
-          <t>6180</t>
+          <t>5082</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Julia Falk</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -12413,10 +12413,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>115983580</v>
+        <v>115983458</v>
       </c>
       <c r="B107" t="n">
-        <v>90306</v>
+        <v>90694</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12425,25 +12425,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5447</v>
+        <v>1506</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12453,10 +12453,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>531462</v>
+        <v>531634</v>
       </c>
       <c r="R107" t="n">
-        <v>7237501</v>
+        <v>7237587</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -12483,12 +12483,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12502,7 +12502,7 @@
       </c>
       <c r="AR107" t="inlineStr">
         <is>
-          <t>5957</t>
+          <t>6180</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -12513,7 +12513,7 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Julia Falk</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -12524,10 +12524,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>115983404</v>
+        <v>115983580</v>
       </c>
       <c r="B108" t="n">
-        <v>57680</v>
+        <v>90306</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12536,43 +12536,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>103001</v>
+        <v>5447</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>bo, hörda ungar</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>531264</v>
+        <v>531462</v>
       </c>
       <c r="R108" t="n">
-        <v>7237712</v>
+        <v>7237501</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12599,12 +12594,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12618,7 +12613,7 @@
       </c>
       <c r="AR108" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5957</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -12629,7 +12624,7 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -12640,10 +12635,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>115983609</v>
+        <v>115983404</v>
       </c>
       <c r="B109" t="n">
-        <v>78589</v>
+        <v>57680</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12656,34 +12651,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>864</v>
+        <v>103001</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>bo, hörda ungar</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>531493</v>
+        <v>531264</v>
       </c>
       <c r="R109" t="n">
-        <v>7237482</v>
+        <v>7237712</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12710,12 +12710,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12729,7 +12729,7 @@
       </c>
       <c r="AR109" t="inlineStr">
         <is>
-          <t>5959</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -12740,7 +12740,7 @@
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -12751,10 +12751,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>115983560</v>
+        <v>115983609</v>
       </c>
       <c r="B110" t="n">
-        <v>77450</v>
+        <v>78589</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12767,21 +12767,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228579</v>
+        <v>864</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12791,10 +12791,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>531571</v>
+        <v>531493</v>
       </c>
       <c r="R110" t="n">
-        <v>7237525</v>
+        <v>7237482</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12821,12 +12821,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="AR110" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>5959</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -12851,7 +12851,7 @@
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Julia Falk</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
@@ -12862,10 +12862,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>115983412</v>
+        <v>115983560</v>
       </c>
       <c r="B111" t="n">
-        <v>77463</v>
+        <v>77450</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12878,21 +12878,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>314</v>
+        <v>228579</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12902,10 +12902,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>531217</v>
+        <v>531571</v>
       </c>
       <c r="R111" t="n">
-        <v>7237675</v>
+        <v>7237525</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -12932,12 +12932,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12951,7 +12951,7 @@
       </c>
       <c r="AR111" t="inlineStr">
         <is>
-          <t>5226</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -12962,7 +12962,7 @@
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Julia Falk</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -12973,7 +12973,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>115983620</v>
+        <v>115983412</v>
       </c>
       <c r="B112" t="n">
         <v>77463</v>
@@ -13013,10 +13013,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>531455</v>
+        <v>531217</v>
       </c>
       <c r="R112" t="n">
-        <v>7237478</v>
+        <v>7237675</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -13043,12 +13043,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13062,7 +13062,7 @@
       </c>
       <c r="AR112" t="inlineStr">
         <is>
-          <t>5949</t>
+          <t>5226</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -13073,7 +13073,7 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Julia Falk</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -13084,10 +13084,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>115983348</v>
+        <v>115983620</v>
       </c>
       <c r="B113" t="n">
-        <v>90359</v>
+        <v>77463</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13100,21 +13100,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5432</v>
+        <v>314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13124,10 +13124,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>531261</v>
+        <v>531455</v>
       </c>
       <c r="R113" t="n">
-        <v>7237846</v>
+        <v>7237478</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="AR113" t="inlineStr">
         <is>
-          <t>5282</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Julia Falk</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -13195,10 +13195,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>115983506</v>
+        <v>115983348</v>
       </c>
       <c r="B114" t="n">
-        <v>90306</v>
+        <v>90359</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13207,25 +13207,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13235,10 +13235,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>530949</v>
+        <v>531261</v>
       </c>
       <c r="R114" t="n">
-        <v>7237563</v>
+        <v>7237846</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -13265,12 +13265,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13284,7 +13284,7 @@
       </c>
       <c r="AR114" t="inlineStr">
         <is>
-          <t>5083</t>
+          <t>5282</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -13306,10 +13306,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>115983517</v>
+        <v>115983506</v>
       </c>
       <c r="B115" t="n">
-        <v>78507</v>
+        <v>90306</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13318,25 +13318,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13346,10 +13346,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>531031</v>
+        <v>530949</v>
       </c>
       <c r="R115" t="n">
-        <v>7237555</v>
+        <v>7237563</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -13395,7 +13395,7 @@
       </c>
       <c r="AR115" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5083</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -13417,7 +13417,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>115983335</v>
+        <v>115983517</v>
       </c>
       <c r="B116" t="n">
         <v>78507</v>
@@ -13457,10 +13457,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>531223</v>
+        <v>531031</v>
       </c>
       <c r="R116" t="n">
-        <v>7237901</v>
+        <v>7237555</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -13487,12 +13487,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13506,7 +13506,7 @@
       </c>
       <c r="AR116" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -13517,10 +13517,121 @@
       </c>
       <c r="AX116" t="inlineStr">
         <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>115983335</v>
+      </c>
+      <c r="B117" t="n">
+        <v>78507</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>531223</v>
+      </c>
+      <c r="R117" t="n">
+        <v>7237901</v>
+      </c>
+      <c r="S117" t="n">
+        <v>5</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2023-06-14</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2023-06-14</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>5280</t>
+        </is>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
           <t>Robin Karlsson</t>
         </is>
       </c>
-      <c r="AY116" t="inlineStr">
+      <c r="AY117" t="inlineStr">
         <is>
           <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
         </is>

--- a/artfynd/A 58919-2024 artfynd.xlsx
+++ b/artfynd/A 58919-2024 artfynd.xlsx
@@ -5338,7 +5338,7 @@
         <v>0</v>
       </c>
       <c r="AE43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG43" t="b">
         <v>0</v>
@@ -10487,7 +10487,7 @@
         <v>0</v>
       </c>
       <c r="AE89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG89" t="b">
         <v>0</v>
@@ -11940,7 +11940,7 @@
         <v>0</v>
       </c>
       <c r="AE102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG102" t="b">
         <v>0</v>
@@ -12944,7 +12944,7 @@
         <v>0</v>
       </c>
       <c r="AE111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG111" t="b">
         <v>0</v>

--- a/artfynd/A 58919-2024 artfynd.xlsx
+++ b/artfynd/A 58919-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY117"/>
+  <dimension ref="A1:AY108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115983558</v>
+        <v>115983444</v>
       </c>
       <c r="B2" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>531587</v>
+        <v>531653</v>
       </c>
       <c r="R2" t="n">
-        <v>7237527</v>
+        <v>7237597</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,7 +759,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>6105</t>
+          <t>6200</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,37 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115983373</v>
+        <v>115983359</v>
       </c>
       <c r="B3" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>531125</v>
+        <v>531262</v>
       </c>
       <c r="R3" t="n">
-        <v>7237803</v>
+        <v>7237832</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -856,12 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,7 +865,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>5213</t>
+          <t>5290</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -886,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -897,37 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115983538</v>
+        <v>115983395</v>
       </c>
       <c r="B4" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>531032</v>
+        <v>531104</v>
       </c>
       <c r="R4" t="n">
-        <v>7237546</v>
+        <v>7237756</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,7 +971,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>5149</t>
+          <t>5154</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1008,37 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115983543</v>
+        <v>115983399</v>
       </c>
       <c r="B5" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>531025</v>
+        <v>531191</v>
       </c>
       <c r="R5" t="n">
-        <v>7237541</v>
+        <v>7237754</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1078,12 +1058,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,7 +1077,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>5084</t>
+          <t>5244</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1108,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1119,37 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115983410</v>
+        <v>115983412</v>
       </c>
       <c r="B6" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1159,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>531207</v>
+        <v>531217</v>
       </c>
       <c r="R6" t="n">
-        <v>7237685</v>
+        <v>7237675</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1208,7 +1183,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>5235</t>
+          <t>5226</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1219,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1230,37 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115983397</v>
+        <v>115983433</v>
       </c>
       <c r="B7" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>531181</v>
+        <v>531621</v>
       </c>
       <c r="R7" t="n">
-        <v>7237755</v>
+        <v>7237607</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1300,12 +1270,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1319,7 +1289,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1330,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Julia Falk</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1341,37 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115983385</v>
+        <v>115983590</v>
       </c>
       <c r="B8" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1381,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>531194</v>
+        <v>531602</v>
       </c>
       <c r="R8" t="n">
-        <v>7237774</v>
+        <v>7237494</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1411,12 +1376,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1430,7 +1395,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>6118</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1441,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Julia Falk</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1452,37 +1417,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115983479</v>
+        <v>115983620</v>
       </c>
       <c r="B9" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1492,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>531764</v>
+        <v>531455</v>
       </c>
       <c r="R9" t="n">
-        <v>7237577</v>
+        <v>7237478</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1522,12 +1482,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,7 +1501,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>6268</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1563,15 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115983433</v>
+        <v>115983411</v>
       </c>
       <c r="B10" t="n">
-        <v>77463</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1579,21 +1534,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>314</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1603,10 +1558,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>531621</v>
+        <v>531220</v>
       </c>
       <c r="R10" t="n">
-        <v>7237607</v>
+        <v>7237675</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1633,12 +1588,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1652,7 +1607,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>5222</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1663,7 +1618,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Julia Falk</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1674,15 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115983413</v>
+        <v>115983338</v>
       </c>
       <c r="B11" t="n">
-        <v>74647</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1690,21 +1640,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1714,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>531214</v>
+        <v>531213</v>
       </c>
       <c r="R11" t="n">
-        <v>7237674</v>
+        <v>7237890</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1763,7 +1713,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>5229</t>
+          <t>5281</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1774,7 +1724,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1785,15 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115983416</v>
+        <v>115944150</v>
       </c>
       <c r="B12" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,39 +1746,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>531611</v>
+        <v>530755</v>
       </c>
       <c r="R12" t="n">
-        <v>7237649</v>
+        <v>7237439</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1860,17 +1800,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-06-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Hackspår på fyra granar</t>
+          <t>2023-06-16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1884,7 +1819,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>6162</t>
+          <t>5694</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1895,7 +1830,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Julia Falk</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1906,37 +1841,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115983402</v>
+        <v>115944186</v>
       </c>
       <c r="B13" t="n">
-        <v>91117</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>918</v>
+        <v>864</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1946,10 +1876,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>531198</v>
+        <v>530966</v>
       </c>
       <c r="R13" t="n">
-        <v>7237748</v>
+        <v>7237384</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1995,7 +1925,7 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5062</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2017,15 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115983408</v>
+        <v>115983327</v>
       </c>
       <c r="B14" t="n">
-        <v>78589</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2057,10 +1982,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>531210</v>
+        <v>531333</v>
       </c>
       <c r="R14" t="n">
-        <v>7237688</v>
+        <v>7237906</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2106,7 +2031,7 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2128,15 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115983434</v>
+        <v>115983352</v>
       </c>
       <c r="B15" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2144,21 +2064,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2168,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>531676</v>
+        <v>531191</v>
       </c>
       <c r="R15" t="n">
-        <v>7237606</v>
+        <v>7237844</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2198,12 +2118,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2217,7 +2137,7 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>6202</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2228,7 +2148,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Julia Falk</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2239,15 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115983399</v>
+        <v>115983394</v>
       </c>
       <c r="B16" t="n">
-        <v>77463</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2255,21 +2170,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>314</v>
+        <v>864</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2279,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>531191</v>
+        <v>531178</v>
       </c>
       <c r="R16" t="n">
-        <v>7237754</v>
+        <v>7237757</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2328,7 +2243,7 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>5244</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2350,15 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115983516</v>
+        <v>115983408</v>
       </c>
       <c r="B17" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,21 +2276,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2390,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>531595</v>
+        <v>531210</v>
       </c>
       <c r="R17" t="n">
-        <v>7237555</v>
+        <v>7237688</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2420,12 +2330,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2439,7 +2349,7 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>6133</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2450,7 +2360,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Julia Falk</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2461,15 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115983376</v>
+        <v>115983414</v>
       </c>
       <c r="B18" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2477,21 +2382,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2501,10 +2406,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>531160</v>
+        <v>531209</v>
       </c>
       <c r="R18" t="n">
-        <v>7237797</v>
+        <v>7237670</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2531,12 +2436,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2550,7 +2455,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>5201</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2561,7 +2466,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2572,55 +2477,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115983366</v>
+        <v>115983418</v>
       </c>
       <c r="B19" t="n">
-        <v>57372</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103031</v>
+        <v>864</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>531156</v>
+        <v>531081</v>
       </c>
       <c r="R19" t="n">
-        <v>7237808</v>
+        <v>7237623</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2655,11 +2550,6 @@
           <t>2023-06-13</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>hörd</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2671,7 +2561,7 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2693,15 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115983388</v>
+        <v>115983541</v>
       </c>
       <c r="B20" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2709,39 +2594,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>531104</v>
+        <v>531587</v>
       </c>
       <c r="R20" t="n">
-        <v>7237769</v>
+        <v>7237543</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2768,17 +2648,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>färska hackmärken</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2792,7 +2667,7 @@
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>6131</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2803,7 +2678,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Julia Falk</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2814,15 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>115983406</v>
+        <v>115983600</v>
       </c>
       <c r="B21" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2830,21 +2700,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2854,10 +2724,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>531275</v>
+        <v>531825</v>
       </c>
       <c r="R21" t="n">
-        <v>7237706</v>
+        <v>7237488</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2884,12 +2754,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2903,7 +2773,7 @@
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2914,7 +2784,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Julia Falk</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2925,37 +2795,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>115983375</v>
+        <v>115983609</v>
       </c>
       <c r="B22" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>864</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2965,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>531150</v>
+        <v>531493</v>
       </c>
       <c r="R22" t="n">
-        <v>7237799</v>
+        <v>7237482</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2995,12 +2860,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3014,7 +2879,7 @@
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>5959</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3025,7 +2890,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3036,37 +2901,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115983590</v>
+        <v>115983402</v>
       </c>
       <c r="B23" t="n">
-        <v>77463</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92721</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>314</v>
+        <v>918</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3076,10 +2936,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>531602</v>
+        <v>531198</v>
       </c>
       <c r="R23" t="n">
-        <v>7237494</v>
+        <v>7237748</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3106,12 +2966,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3125,7 +2985,7 @@
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>6118</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3136,7 +2996,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Julia Falk</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3147,15 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115983345</v>
+        <v>115983337</v>
       </c>
       <c r="B24" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3163,21 +3018,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3187,10 +3042,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>531269</v>
+        <v>531199</v>
       </c>
       <c r="R24" t="n">
-        <v>7237876</v>
+        <v>7237894</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3236,7 +3091,7 @@
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>5283</t>
+          <t>5276</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3258,15 +3113,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115983509</v>
+        <v>115983634</v>
       </c>
       <c r="B25" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3274,21 +3124,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3298,10 +3148,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>531050</v>
+        <v>531456</v>
       </c>
       <c r="R25" t="n">
-        <v>7237557</v>
+        <v>7237464</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3328,12 +3178,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3347,7 +3197,7 @@
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>5096</t>
+          <t>5951</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3358,7 +3208,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Julia Falk</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3369,15 +3219,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115983566</v>
+        <v>115983354</v>
       </c>
       <c r="B26" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3385,21 +3230,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3409,10 +3254,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>531539</v>
+        <v>531311</v>
       </c>
       <c r="R26" t="n">
-        <v>7237512</v>
+        <v>7237842</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3439,12 +3284,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3458,7 +3303,7 @@
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>6079</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3469,7 +3314,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Julia Falk</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3480,37 +3325,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>115983463</v>
+        <v>115983364</v>
       </c>
       <c r="B27" t="n">
-        <v>91272</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4769</v>
+        <v>1204</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3520,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>531493</v>
+        <v>531117</v>
       </c>
       <c r="R27" t="n">
-        <v>7237586</v>
+        <v>7237812</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3550,12 +3390,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3569,7 +3409,7 @@
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>5997</t>
+          <t>5207</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3580,7 +3420,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3591,37 +3431,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>115983545</v>
+        <v>115983390</v>
       </c>
       <c r="B28" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3631,10 +3466,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>531529</v>
+        <v>531079</v>
       </c>
       <c r="R28" t="n">
-        <v>7237539</v>
+        <v>7237768</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3661,12 +3496,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3680,7 +3515,7 @@
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>5969</t>
+          <t>5153</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3691,7 +3526,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3702,37 +3537,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>115983415</v>
+        <v>115983577</v>
       </c>
       <c r="B29" t="n">
-        <v>79593</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>1204</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3742,10 +3572,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>531602</v>
+        <v>531711</v>
       </c>
       <c r="R29" t="n">
-        <v>7237662</v>
+        <v>7237505</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3791,7 +3621,7 @@
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>6229</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3813,37 +3643,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>115983343</v>
+        <v>115983628</v>
       </c>
       <c r="B30" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3853,10 +3678,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>531313</v>
+        <v>531463</v>
       </c>
       <c r="R30" t="n">
-        <v>7237880</v>
+        <v>7237468</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3883,12 +3708,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3902,7 +3727,7 @@
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5960</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3913,7 +3738,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3924,37 +3749,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>115983528</v>
+        <v>115983331</v>
       </c>
       <c r="B31" t="n">
-        <v>93881</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1004670</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tuffmossor</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Palustriella</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Ochyra</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3964,10 +3784,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>531525</v>
+        <v>531180</v>
       </c>
       <c r="R31" t="n">
-        <v>7237551</v>
+        <v>7237903</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3994,12 +3814,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4013,7 +3833,7 @@
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>6004</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4024,7 +3844,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -4035,15 +3855,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>115983352</v>
+        <v>115983345</v>
       </c>
       <c r="B32" t="n">
-        <v>78589</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4051,21 +3866,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4075,10 +3890,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>531191</v>
+        <v>531269</v>
       </c>
       <c r="R32" t="n">
-        <v>7237844</v>
+        <v>7237876</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4124,7 +3939,7 @@
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>5283</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4135,7 +3950,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4146,15 +3961,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>115983409</v>
+        <v>115983347</v>
       </c>
       <c r="B33" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4186,10 +3996,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>531223</v>
+        <v>531185</v>
       </c>
       <c r="R33" t="n">
-        <v>7237685</v>
+        <v>7237854</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4235,7 +4045,7 @@
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>5233</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4246,7 +4056,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4257,15 +4067,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>115983347</v>
+        <v>115983360</v>
       </c>
       <c r="B34" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4297,10 +4102,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>531185</v>
+        <v>531286</v>
       </c>
       <c r="R34" t="n">
-        <v>7237854</v>
+        <v>7237827</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4346,7 +4151,7 @@
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4368,15 +4173,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>115983360</v>
+        <v>115983363</v>
       </c>
       <c r="B35" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4408,10 +4208,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>531286</v>
+        <v>531137</v>
       </c>
       <c r="R35" t="n">
-        <v>7237827</v>
+        <v>7237817</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4438,12 +4238,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4457,7 +4257,7 @@
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>5291</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4479,15 +4279,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>115983414</v>
+        <v>115983365</v>
       </c>
       <c r="B36" t="n">
-        <v>78589</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4495,21 +4290,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4519,10 +4314,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>531209</v>
+        <v>531347</v>
       </c>
       <c r="R36" t="n">
-        <v>7237670</v>
+        <v>7237811</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4568,7 +4363,7 @@
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>5303</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4579,7 +4374,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4590,37 +4385,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>115983540</v>
+        <v>115983374</v>
       </c>
       <c r="B37" t="n">
-        <v>93885</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2699</v>
+        <v>1312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Klotuffmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Palustriella falcata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Brid.) Hedenäs</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4630,10 +4420,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>531527</v>
+        <v>531164</v>
       </c>
       <c r="R37" t="n">
-        <v>7237545</v>
+        <v>7237801</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4660,12 +4450,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4679,7 +4469,7 @@
       </c>
       <c r="AR37" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>5202</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4690,7 +4480,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4701,15 +4491,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>115983364</v>
+        <v>115983385</v>
       </c>
       <c r="B38" t="n">
-        <v>90355</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4717,21 +4502,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4741,10 +4526,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>531117</v>
+        <v>531194</v>
       </c>
       <c r="R38" t="n">
-        <v>7237812</v>
+        <v>7237774</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4790,7 +4575,7 @@
       </c>
       <c r="AR38" t="inlineStr">
         <is>
-          <t>5207</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4812,15 +4597,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>115983419</v>
+        <v>115983401</v>
       </c>
       <c r="B39" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4852,10 +4632,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>531039</v>
+        <v>531208</v>
       </c>
       <c r="R39" t="n">
-        <v>7237623</v>
+        <v>7237752</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4882,12 +4662,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4901,7 +4681,7 @@
       </c>
       <c r="AR39" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5240</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4923,15 +4703,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>115983467</v>
+        <v>115983409</v>
       </c>
       <c r="B40" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4963,10 +4738,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>531494</v>
+        <v>531223</v>
       </c>
       <c r="R40" t="n">
-        <v>7237585</v>
+        <v>7237685</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4993,12 +4768,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5012,7 +4787,7 @@
       </c>
       <c r="AR40" t="inlineStr">
         <is>
-          <t>5993</t>
+          <t>5233</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5023,7 +4798,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -5034,15 +4809,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>115983390</v>
+        <v>115983419</v>
       </c>
       <c r="B41" t="n">
-        <v>90355</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5050,21 +4820,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5074,10 +4844,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>531079</v>
+        <v>531039</v>
       </c>
       <c r="R41" t="n">
-        <v>7237768</v>
+        <v>7237623</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5123,7 +4893,7 @@
       </c>
       <c r="AR41" t="inlineStr">
         <is>
-          <t>5153</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5145,15 +4915,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>115983377</v>
+        <v>115983423</v>
       </c>
       <c r="B42" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5161,21 +4926,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5185,10 +4950,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>531152</v>
+        <v>531083</v>
       </c>
       <c r="R42" t="n">
-        <v>7237795</v>
+        <v>7237621</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5215,12 +4980,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5234,7 +4999,7 @@
       </c>
       <c r="AR42" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>5103</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5245,7 +5010,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5256,15 +5021,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>115983588</v>
+        <v>115983467</v>
       </c>
       <c r="B43" t="n">
-        <v>77450</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5272,21 +5032,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228579</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5296,10 +5056,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>531675</v>
+        <v>531494</v>
       </c>
       <c r="R43" t="n">
-        <v>7237497</v>
+        <v>7237585</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5326,26 +5086,26 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AR43" t="inlineStr">
         <is>
-          <t>6220</t>
+          <t>5993</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5356,7 +5116,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Julia Falk</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5367,15 +5127,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>115983395</v>
+        <v>115983505</v>
       </c>
       <c r="B44" t="n">
-        <v>77463</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5383,21 +5138,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>314</v>
+        <v>1312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5407,10 +5162,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>531104</v>
+        <v>531002</v>
       </c>
       <c r="R44" t="n">
-        <v>7237756</v>
+        <v>7237563</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5456,7 +5211,7 @@
       </c>
       <c r="AR44" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5478,15 +5233,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>115983423</v>
+        <v>115983509</v>
       </c>
       <c r="B45" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5518,10 +5268,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>531083</v>
+        <v>531050</v>
       </c>
       <c r="R45" t="n">
-        <v>7237621</v>
+        <v>7237557</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5567,7 +5317,7 @@
       </c>
       <c r="AR45" t="inlineStr">
         <is>
-          <t>5103</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5589,15 +5339,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>115983453</v>
+        <v>115983525</v>
       </c>
       <c r="B46" t="n">
-        <v>74652</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5605,21 +5350,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1467</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5629,10 +5374,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>531654</v>
+        <v>530980</v>
       </c>
       <c r="R46" t="n">
-        <v>7237592</v>
+        <v>7237552</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5659,12 +5404,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5678,7 +5423,7 @@
       </c>
       <c r="AR46" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>5082</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5689,7 +5434,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Julia Falk</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5700,37 +5445,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>115983570</v>
+        <v>115983529</v>
       </c>
       <c r="B47" t="n">
-        <v>93496</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1004672</v>
+        <v>1312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Källmossor</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Philonotis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Brid.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5740,10 +5480,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>531614</v>
+        <v>531062</v>
       </c>
       <c r="R47" t="n">
-        <v>7237509</v>
+        <v>7237551</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5770,12 +5510,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5789,7 +5529,7 @@
       </c>
       <c r="AR47" t="inlineStr">
         <is>
-          <t>6127</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5800,7 +5540,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Julia Falk</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5811,15 +5551,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>115983492</v>
+        <v>115983538</v>
       </c>
       <c r="B48" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5827,21 +5562,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5851,10 +5586,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>531845</v>
+        <v>531032</v>
       </c>
       <c r="R48" t="n">
-        <v>7237568</v>
+        <v>7237546</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5881,12 +5616,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5900,7 +5635,7 @@
       </c>
       <c r="AR48" t="inlineStr">
         <is>
-          <t>6284</t>
+          <t>5149</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5911,7 +5646,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Julia Falk</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5922,15 +5657,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>115983362</v>
+        <v>115983552</v>
       </c>
       <c r="B49" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5938,21 +5668,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5962,10 +5692,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>531285</v>
+        <v>531842</v>
       </c>
       <c r="R49" t="n">
-        <v>7237817</v>
+        <v>7237536</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5992,12 +5722,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6011,7 +5741,7 @@
       </c>
       <c r="AR49" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>6280</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6022,7 +5752,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Julia Falk</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -6033,59 +5763,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>115983417</v>
+        <v>115983566</v>
       </c>
       <c r="B50" t="n">
-        <v>57372</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103031</v>
+        <v>1312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>531055</v>
+        <v>531539</v>
       </c>
       <c r="R50" t="n">
-        <v>7237630</v>
+        <v>7237512</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6112,17 +5828,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>på torrbjörk</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6136,7 +5847,7 @@
       </c>
       <c r="AR50" t="inlineStr">
         <is>
-          <t>5114</t>
+          <t>6079</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6147,7 +5858,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Julia Falk</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6158,15 +5869,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>115944150</v>
+        <v>115983367</v>
       </c>
       <c r="B51" t="n">
-        <v>78589</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6174,21 +5880,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>864</v>
+        <v>1467</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6198,10 +5904,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>530755</v>
+        <v>531300</v>
       </c>
       <c r="R51" t="n">
-        <v>7237439</v>
+        <v>7237806</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6228,12 +5934,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2023-06-16</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2023-06-16</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6247,7 +5953,7 @@
       </c>
       <c r="AR51" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>5293</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6258,7 +5964,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6269,15 +5975,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>115983606</v>
+        <v>115983453</v>
       </c>
       <c r="B52" t="n">
-        <v>74652</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6309,10 +6010,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>531455</v>
+        <v>531654</v>
       </c>
       <c r="R52" t="n">
-        <v>7237484</v>
+        <v>7237592</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6339,12 +6040,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6358,7 +6059,7 @@
       </c>
       <c r="AR52" t="inlineStr">
         <is>
-          <t>5955</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6369,7 +6070,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Julia Falk</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6380,15 +6081,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>115983628</v>
+        <v>115983606</v>
       </c>
       <c r="B53" t="n">
-        <v>90355</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6396,21 +6092,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1204</v>
+        <v>1467</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6420,10 +6116,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>531463</v>
+        <v>531455</v>
       </c>
       <c r="R53" t="n">
-        <v>7237468</v>
+        <v>7237484</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6469,7 +6165,7 @@
       </c>
       <c r="AR53" t="inlineStr">
         <is>
-          <t>5960</t>
+          <t>5955</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6491,37 +6187,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>115983457</v>
+        <v>115983458</v>
       </c>
       <c r="B54" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92292</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>1506</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6531,10 +6222,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>530978</v>
+        <v>531634</v>
       </c>
       <c r="R54" t="n">
-        <v>7237588</v>
+        <v>7237587</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6561,12 +6252,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6580,7 +6271,7 @@
       </c>
       <c r="AR54" t="inlineStr">
         <is>
-          <t>5097</t>
+          <t>6180</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6591,7 +6282,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Julia Falk</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6602,59 +6293,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>115983340</v>
+        <v>115983479</v>
       </c>
       <c r="B55" t="n">
-        <v>97680</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>531296</v>
+        <v>531764</v>
       </c>
       <c r="R55" t="n">
-        <v>7237887</v>
+        <v>7237577</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6681,12 +6358,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6700,7 +6377,7 @@
       </c>
       <c r="AR55" t="inlineStr">
         <is>
-          <t>5310</t>
+          <t>6268</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6711,7 +6388,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Julia Falk</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6722,15 +6399,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>115983529</v>
+        <v>115983543</v>
       </c>
       <c r="B56" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6738,21 +6410,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6762,10 +6434,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>531062</v>
+        <v>531025</v>
       </c>
       <c r="R56" t="n">
-        <v>7237551</v>
+        <v>7237541</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6811,7 +6483,7 @@
       </c>
       <c r="AR56" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>5084</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6833,15 +6505,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>115983555</v>
+        <v>115983540</v>
       </c>
       <c r="B57" t="n">
-        <v>93496</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96155</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6849,21 +6516,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1004672</v>
+        <v>2699</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Källmossor</t>
+          <t>Klotuffmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Philonotis</t>
+          <t>Palustriella falcata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Brid.</t>
+          <t>(Brid.) Hedenäs</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6873,10 +6540,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>531569</v>
+        <v>531527</v>
       </c>
       <c r="R57" t="n">
-        <v>7237534</v>
+        <v>7237545</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6903,12 +6570,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-30</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-30</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6922,7 +6589,7 @@
       </c>
       <c r="AR57" t="inlineStr">
         <is>
-          <t>6099</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -6933,7 +6600,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Julia Falk</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6944,55 +6611,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>115983391</v>
+        <v>115983621</v>
       </c>
       <c r="B58" t="n">
-        <v>56115</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100077</v>
+        <v>2809</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Utter</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lutra lutra</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>531175</v>
+        <v>531190</v>
       </c>
       <c r="R58" t="n">
-        <v>7237761</v>
+        <v>7237477</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7019,12 +6676,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7038,7 +6695,7 @@
       </c>
       <c r="AR58" t="inlineStr">
         <is>
-          <t>5255</t>
+          <t>5875</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7049,7 +6706,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -7060,37 +6717,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>115983552</v>
+        <v>115983624</v>
       </c>
       <c r="B59" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1312</v>
+        <v>2809</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7100,10 +6752,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>531842</v>
+        <v>531040</v>
       </c>
       <c r="R59" t="n">
-        <v>7237536</v>
+        <v>7237470</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7130,12 +6782,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7149,7 +6801,7 @@
       </c>
       <c r="AR59" t="inlineStr">
         <is>
-          <t>6280</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7160,7 +6812,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Julia Falk</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7171,37 +6823,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>115983374</v>
+        <v>115983463</v>
       </c>
       <c r="B60" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1312</v>
+        <v>4769</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7211,10 +6858,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>531164</v>
+        <v>531493</v>
       </c>
       <c r="R60" t="n">
-        <v>7237801</v>
+        <v>7237586</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7241,12 +6888,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7260,7 +6907,7 @@
       </c>
       <c r="AR60" t="inlineStr">
         <is>
-          <t>5202</t>
+          <t>5997</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7271,7 +6918,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7282,37 +6929,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>115983601</v>
+        <v>115983611</v>
       </c>
       <c r="B61" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>4769</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7322,10 +6964,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>531048</v>
+        <v>531453</v>
       </c>
       <c r="R61" t="n">
-        <v>7237487</v>
+        <v>7237481</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7352,12 +6994,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7371,7 +7013,7 @@
       </c>
       <c r="AR61" t="inlineStr">
         <is>
-          <t>5221</t>
+          <t>5945</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7382,7 +7024,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Julia Falk</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7393,37 +7035,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>115983358</v>
+        <v>115983506</v>
       </c>
       <c r="B62" t="n">
-        <v>74647</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7433,10 +7070,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>531265</v>
+        <v>530949</v>
       </c>
       <c r="R62" t="n">
-        <v>7237833</v>
+        <v>7237563</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7463,12 +7100,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7482,7 +7119,7 @@
       </c>
       <c r="AR62" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5083</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7493,7 +7130,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7504,15 +7141,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>115983476</v>
+        <v>115983580</v>
       </c>
       <c r="B63" t="n">
-        <v>5185</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7520,39 +7152,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>105930</v>
+        <v>5447</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>531576</v>
+        <v>531462</v>
       </c>
       <c r="R63" t="n">
-        <v>7237581</v>
+        <v>7237501</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7579,12 +7206,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7598,7 +7225,7 @@
       </c>
       <c r="AR63" t="inlineStr">
         <is>
-          <t>6136</t>
+          <t>5957</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7609,7 +7236,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Julia Falk</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7620,37 +7247,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>115983577</v>
+        <v>115944184</v>
       </c>
       <c r="B64" t="n">
-        <v>90355</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7660,10 +7282,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>531711</v>
+        <v>530906</v>
       </c>
       <c r="R64" t="n">
-        <v>7237505</v>
+        <v>7237385</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7690,12 +7312,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7709,7 +7331,7 @@
       </c>
       <c r="AR64" t="inlineStr">
         <is>
-          <t>6229</t>
+          <t>5061</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7720,7 +7342,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Julia Falk</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7731,37 +7353,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>115983367</v>
+        <v>115983335</v>
       </c>
       <c r="B65" t="n">
-        <v>74652</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7771,10 +7388,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>531300</v>
+        <v>531223</v>
       </c>
       <c r="R65" t="n">
-        <v>7237806</v>
+        <v>7237901</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7820,7 +7437,7 @@
       </c>
       <c r="AR65" t="inlineStr">
         <is>
-          <t>5293</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7842,37 +7459,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>115983398</v>
+        <v>115983343</v>
       </c>
       <c r="B66" t="n">
-        <v>74647</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7882,10 +7494,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>531193</v>
+        <v>531313</v>
       </c>
       <c r="R66" t="n">
-        <v>7237754</v>
+        <v>7237880</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7931,7 +7543,7 @@
       </c>
       <c r="AR66" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -7953,37 +7565,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>115983624</v>
+        <v>115983350</v>
       </c>
       <c r="B67" t="n">
-        <v>94068</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7993,10 +7600,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>531040</v>
+        <v>531193</v>
       </c>
       <c r="R67" t="n">
-        <v>7237470</v>
+        <v>7237846</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8042,7 +7649,7 @@
       </c>
       <c r="AR67" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8064,37 +7671,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>115983411</v>
+        <v>115983356</v>
       </c>
       <c r="B68" t="n">
-        <v>86661</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8104,10 +7706,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>531220</v>
+        <v>531326</v>
       </c>
       <c r="R68" t="n">
-        <v>7237675</v>
+        <v>7237839</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8153,7 +7755,7 @@
       </c>
       <c r="AR68" t="inlineStr">
         <is>
-          <t>5222</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8164,7 +7766,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8175,37 +7777,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>115983342</v>
+        <v>115983362</v>
       </c>
       <c r="B69" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8215,10 +7812,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>531208</v>
+        <v>531285</v>
       </c>
       <c r="R69" t="n">
-        <v>7237884</v>
+        <v>7237817</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8264,7 +7861,7 @@
       </c>
       <c r="AR69" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8275,7 +7872,7 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -8286,37 +7883,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>115983372</v>
+        <v>115983377</v>
       </c>
       <c r="B70" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8326,10 +7918,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>531128</v>
+        <v>531152</v>
       </c>
       <c r="R70" t="n">
-        <v>7237804</v>
+        <v>7237795</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8356,12 +7948,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8375,7 +7967,7 @@
       </c>
       <c r="AR70" t="inlineStr">
         <is>
-          <t>5208</t>
+          <t>5267</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8386,7 +7978,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -8397,19 +7989,14 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>115983420</v>
+        <v>115983403</v>
       </c>
       <c r="B71" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -8437,10 +8024,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>531038</v>
+        <v>531210</v>
       </c>
       <c r="R71" t="n">
-        <v>7237622</v>
+        <v>7237736</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8467,12 +8054,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8486,7 +8073,7 @@
       </c>
       <c r="AR71" t="inlineStr">
         <is>
-          <t>5098</t>
+          <t>5257</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8497,7 +8084,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8508,37 +8095,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>115983331</v>
+        <v>115983420</v>
       </c>
       <c r="B72" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8548,10 +8130,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>531180</v>
+        <v>531038</v>
       </c>
       <c r="R72" t="n">
-        <v>7237903</v>
+        <v>7237622</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8578,12 +8160,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8597,7 +8179,7 @@
       </c>
       <c r="AR72" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>5098</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8619,37 +8201,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>115983401</v>
+        <v>115983517</v>
       </c>
       <c r="B73" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8659,10 +8236,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>531208</v>
+        <v>531031</v>
       </c>
       <c r="R73" t="n">
-        <v>7237752</v>
+        <v>7237555</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8689,12 +8266,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8708,7 +8285,7 @@
       </c>
       <c r="AR73" t="inlineStr">
         <is>
-          <t>5240</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8730,37 +8307,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>115983418</v>
+        <v>115983558</v>
       </c>
       <c r="B74" t="n">
-        <v>78589</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8770,10 +8342,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>531081</v>
+        <v>531587</v>
       </c>
       <c r="R74" t="n">
-        <v>7237623</v>
+        <v>7237527</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8800,12 +8372,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8819,7 +8391,7 @@
       </c>
       <c r="AR74" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>6105</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -8830,7 +8402,7 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Julia Falk</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8841,15 +8413,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>115983507</v>
+        <v>115983329</v>
       </c>
       <c r="B75" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8857,39 +8424,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>531005</v>
+        <v>531198</v>
       </c>
       <c r="R75" t="n">
-        <v>7237562</v>
+        <v>7237905</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8916,17 +8478,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>hackmärken</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8940,7 +8497,7 @@
       </c>
       <c r="AR75" t="inlineStr">
         <is>
-          <t>5074</t>
+          <t>5275</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -8951,7 +8508,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8962,15 +8519,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>115944186</v>
+        <v>115983344</v>
       </c>
       <c r="B76" t="n">
-        <v>78589</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8978,21 +8530,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>864</v>
+        <v>6440</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9002,10 +8554,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>530966</v>
+        <v>531276</v>
       </c>
       <c r="R76" t="n">
-        <v>7237384</v>
+        <v>7237880</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9032,12 +8584,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9051,7 +8603,7 @@
       </c>
       <c r="AR76" t="inlineStr">
         <is>
-          <t>5062</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9062,7 +8614,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -9073,15 +8625,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>115983337</v>
+        <v>115983358</v>
       </c>
       <c r="B77" t="n">
-        <v>90337</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9089,21 +8636,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9113,10 +8660,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>531199</v>
+        <v>531265</v>
       </c>
       <c r="R77" t="n">
-        <v>7237894</v>
+        <v>7237833</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9162,7 +8709,7 @@
       </c>
       <c r="AR77" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9173,7 +8720,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -9184,37 +8731,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>115983611</v>
+        <v>115983398</v>
       </c>
       <c r="B78" t="n">
-        <v>91272</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4769</v>
+        <v>6440</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9224,10 +8766,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>531453</v>
+        <v>531193</v>
       </c>
       <c r="R78" t="n">
-        <v>7237481</v>
+        <v>7237754</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9254,12 +8796,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9273,7 +8815,7 @@
       </c>
       <c r="AR78" t="inlineStr">
         <is>
-          <t>5945</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9284,7 +8826,7 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Julia Falk</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -9295,15 +8837,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>115983584</v>
+        <v>115983413</v>
       </c>
       <c r="B79" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9311,21 +8848,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9335,10 +8872,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>531469</v>
+        <v>531214</v>
       </c>
       <c r="R79" t="n">
-        <v>7237499</v>
+        <v>7237674</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9365,12 +8902,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9384,7 +8921,7 @@
       </c>
       <c r="AR79" t="inlineStr">
         <is>
-          <t>5956</t>
+          <t>5229</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9395,7 +8932,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -9406,37 +8943,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>115983344</v>
+        <v>115983368</v>
       </c>
       <c r="B80" t="n">
-        <v>74647</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9446,10 +8978,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>531276</v>
+        <v>531303</v>
       </c>
       <c r="R80" t="n">
-        <v>7237880</v>
+        <v>7237805</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9495,7 +9027,7 @@
       </c>
       <c r="AR80" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>5294</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9517,37 +9049,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>115983329</v>
+        <v>115983373</v>
       </c>
       <c r="B81" t="n">
-        <v>74647</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9557,10 +9084,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>531198</v>
+        <v>531125</v>
       </c>
       <c r="R81" t="n">
-        <v>7237905</v>
+        <v>7237803</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9587,12 +9114,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9606,7 +9133,7 @@
       </c>
       <c r="AR81" t="inlineStr">
         <is>
-          <t>5275</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9617,7 +9144,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9628,37 +9155,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>115983333</v>
+        <v>115983375</v>
       </c>
       <c r="B82" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9668,10 +9190,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>531185</v>
+        <v>531150</v>
       </c>
       <c r="R82" t="n">
-        <v>7237902</v>
+        <v>7237799</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9717,7 +9239,7 @@
       </c>
       <c r="AR82" t="inlineStr">
         <is>
-          <t>5273</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9728,7 +9250,7 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9739,37 +9261,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>115983356</v>
+        <v>115983397</v>
       </c>
       <c r="B83" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9779,10 +9296,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>531326</v>
+        <v>531181</v>
       </c>
       <c r="R83" t="n">
-        <v>7237839</v>
+        <v>7237755</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9828,7 +9345,7 @@
       </c>
       <c r="AR83" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -9850,37 +9367,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>115983478</v>
+        <v>115983593</v>
       </c>
       <c r="B84" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9890,10 +9402,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>531590</v>
+        <v>531476</v>
       </c>
       <c r="R84" t="n">
-        <v>7237578</v>
+        <v>7237493</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9920,12 +9432,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9939,7 +9451,7 @@
       </c>
       <c r="AR84" t="inlineStr">
         <is>
-          <t>6138</t>
+          <t>5958</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -9950,7 +9462,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Julia Falk</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9961,15 +9473,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>115983368</v>
+        <v>115983608</v>
       </c>
       <c r="B85" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10001,10 +9508,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>531303</v>
+        <v>531728</v>
       </c>
       <c r="R85" t="n">
-        <v>7237805</v>
+        <v>7237482</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -10031,12 +9538,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10050,7 +9557,7 @@
       </c>
       <c r="AR85" t="inlineStr">
         <is>
-          <t>5294</t>
+          <t>6470</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10061,7 +9568,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Julia Falk</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -10072,37 +9579,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>115983338</v>
+        <v>115983643</v>
       </c>
       <c r="B86" t="n">
-        <v>90624</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10112,10 +9614,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>531213</v>
+        <v>531534</v>
       </c>
       <c r="R86" t="n">
-        <v>7237890</v>
+        <v>7237455</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10142,12 +9644,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10161,7 +9663,7 @@
       </c>
       <c r="AR86" t="inlineStr">
         <is>
-          <t>5281</t>
+          <t>6047</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10172,7 +9674,7 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Julia Falk</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -10183,37 +9685,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>115983354</v>
+        <v>115983415</v>
       </c>
       <c r="B87" t="n">
-        <v>90341</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10223,10 +9720,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>531311</v>
+        <v>531602</v>
       </c>
       <c r="R87" t="n">
-        <v>7237842</v>
+        <v>7237662</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10253,12 +9750,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10272,7 +9769,7 @@
       </c>
       <c r="AR87" t="inlineStr">
         <is>
-          <t>5304</t>
+          <t>6171</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -10283,7 +9780,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Julia Falk</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -10294,15 +9791,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>115983521</v>
+        <v>115983639</v>
       </c>
       <c r="B88" t="n">
-        <v>93496</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10310,21 +9802,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1004672</v>
+        <v>6463</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Källmossor</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Philonotis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10334,10 +9826,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>531530</v>
+        <v>531533</v>
       </c>
       <c r="R88" t="n">
-        <v>7237553</v>
+        <v>7237459</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10364,12 +9856,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10383,7 +9875,7 @@
       </c>
       <c r="AR88" t="inlineStr">
         <is>
-          <t>5977</t>
+          <t>6046</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -10394,7 +9886,7 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Julia Falk</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -10405,50 +9897,50 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>115983466</v>
+        <v>115983391</v>
       </c>
       <c r="B89" t="n">
-        <v>77450</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56766</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228579</v>
+        <v>100077</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Utter</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lutra lutra</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>531495</v>
+        <v>531175</v>
       </c>
       <c r="R89" t="n">
-        <v>7237585</v>
+        <v>7237761</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10475,26 +9967,26 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AR89" t="inlineStr">
         <is>
-          <t>5992</t>
+          <t>5255</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -10505,7 +9997,7 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -10516,15 +10008,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>115944182</v>
+        <v>115983381</v>
       </c>
       <c r="B90" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10532,34 +10019,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>530964</v>
+        <v>531280</v>
       </c>
       <c r="R90" t="n">
-        <v>7237399</v>
+        <v>7237776</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10586,12 +10078,17 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-06-14</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>hackmärken</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10605,7 +10102,7 @@
       </c>
       <c r="AR90" t="inlineStr">
         <is>
-          <t>5064</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -10627,15 +10124,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>115983346</v>
+        <v>115983388</v>
       </c>
       <c r="B91" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10643,34 +10135,39 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>531304</v>
+        <v>531104</v>
       </c>
       <c r="R91" t="n">
-        <v>7237855</v>
+        <v>7237769</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10697,12 +10194,17 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-06-13</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>färska hackmärken</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10716,7 +10218,7 @@
       </c>
       <c r="AR91" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>5172</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -10738,15 +10240,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>115983350</v>
+        <v>115983416</v>
       </c>
       <c r="B92" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10754,34 +10251,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>531193</v>
+        <v>531611</v>
       </c>
       <c r="R92" t="n">
-        <v>7237846</v>
+        <v>7237649</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10808,12 +10310,17 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Hackspår på fyra granar</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10827,7 +10334,7 @@
       </c>
       <c r="AR92" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>6162</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -10838,7 +10345,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Julia Falk</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10849,15 +10356,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>115983359</v>
+        <v>115983507</v>
       </c>
       <c r="B93" t="n">
-        <v>77463</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10865,34 +10367,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>314</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>531262</v>
+        <v>531005</v>
       </c>
       <c r="R93" t="n">
-        <v>7237832</v>
+        <v>7237562</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10919,12 +10426,17 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-06-13</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>hackmärken</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10938,7 +10450,7 @@
       </c>
       <c r="AR93" t="inlineStr">
         <is>
-          <t>5290</t>
+          <t>5074</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -10949,7 +10461,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10960,15 +10472,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>115983381</v>
+        <v>115983605</v>
       </c>
       <c r="B94" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11005,10 +10512,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>531280</v>
+        <v>531778</v>
       </c>
       <c r="R94" t="n">
-        <v>7237776</v>
+        <v>7237484</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11035,17 +10542,17 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>hackmärken</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11059,7 +10566,7 @@
       </c>
       <c r="AR94" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>6467</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11070,7 +10577,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Julia Falk</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -11081,15 +10588,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>115983403</v>
+        <v>115983404</v>
       </c>
       <c r="B95" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58388</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11097,34 +10599,39 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>103001</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>bo, hörda ungar</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>531210</v>
+        <v>531264</v>
       </c>
       <c r="R95" t="n">
-        <v>7237736</v>
+        <v>7237712</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11170,7 +10677,7 @@
       </c>
       <c r="AR95" t="inlineStr">
         <is>
-          <t>5257</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -11181,7 +10688,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -11192,15 +10699,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>115983444</v>
+        <v>115983366</v>
       </c>
       <c r="B96" t="n">
-        <v>90288</v>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11208,34 +10710,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>112</v>
+        <v>103031</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>531653</v>
+        <v>531156</v>
       </c>
       <c r="R96" t="n">
-        <v>7237597</v>
+        <v>7237808</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11262,12 +10769,17 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-06-13</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>hörd</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11281,7 +10793,7 @@
       </c>
       <c r="AR96" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -11292,7 +10804,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Julia Falk</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -11303,15 +10815,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>115983541</v>
+        <v>115983417</v>
       </c>
       <c r="B97" t="n">
-        <v>78589</v>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11319,34 +10826,43 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>864</v>
+        <v>103031</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>531587</v>
+        <v>531055</v>
       </c>
       <c r="R97" t="n">
-        <v>7237543</v>
+        <v>7237630</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11373,12 +10889,17 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-06-13</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>på torrbjörk</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11392,7 +10913,7 @@
       </c>
       <c r="AR97" t="inlineStr">
         <is>
-          <t>6131</t>
+          <t>5114</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -11403,7 +10924,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Julia Falk</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -11414,15 +10935,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>115983593</v>
+        <v>115983476</v>
       </c>
       <c r="B98" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11430,34 +10946,39 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6462</v>
+        <v>105930</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>531476</v>
+        <v>531576</v>
       </c>
       <c r="R98" t="n">
-        <v>7237493</v>
+        <v>7237581</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11484,12 +11005,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11503,7 +11024,7 @@
       </c>
       <c r="AR98" t="inlineStr">
         <is>
-          <t>5958</t>
+          <t>6136</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -11514,7 +11035,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Julia Falk</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -11525,50 +11046,50 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>115983363</v>
+        <v>115983633</v>
       </c>
       <c r="B99" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1312</v>
+        <v>105930</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>531137</v>
+        <v>531480</v>
       </c>
       <c r="R99" t="n">
-        <v>7237817</v>
+        <v>7237465</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11595,12 +11116,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11614,7 +11135,7 @@
       </c>
       <c r="AR99" t="inlineStr">
         <is>
-          <t>5206</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -11625,7 +11146,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Julia Falk</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -11636,50 +11157,54 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>115983369</v>
+        <v>115983340</v>
       </c>
       <c r="B100" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>531319</v>
+        <v>531296</v>
       </c>
       <c r="R100" t="n">
-        <v>7237804</v>
+        <v>7237887</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11725,7 +11250,7 @@
       </c>
       <c r="AR100" t="inlineStr">
         <is>
-          <t>5297</t>
+          <t>5310</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -11747,15 +11272,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>115983586</v>
+        <v>115983466</v>
       </c>
       <c r="B101" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78339</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11763,21 +11283,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11787,10 +11307,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>531653</v>
+        <v>531495</v>
       </c>
       <c r="R101" t="n">
-        <v>7237498</v>
+        <v>7237585</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11817,26 +11337,26 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AR101" t="inlineStr">
         <is>
-          <t>6212</t>
+          <t>5992</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -11847,7 +11367,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Julia Falk</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11858,15 +11378,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>115983616</v>
+        <v>115983560</v>
       </c>
       <c r="B102" t="n">
-        <v>77450</v>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78339</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11898,10 +11413,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>531457</v>
+        <v>531571</v>
       </c>
       <c r="R102" t="n">
-        <v>7237480</v>
+        <v>7237525</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -11928,12 +11443,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11947,7 +11462,7 @@
       </c>
       <c r="AR102" t="inlineStr">
         <is>
-          <t>5947</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -11969,15 +11484,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>115983383</v>
+        <v>115983588</v>
       </c>
       <c r="B103" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78339</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11985,21 +11495,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12009,10 +11519,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>531194</v>
+        <v>531675</v>
       </c>
       <c r="R103" t="n">
-        <v>7237776</v>
+        <v>7237497</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12039,26 +11549,26 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
       <c r="AE103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
       <c r="AR103" t="inlineStr">
         <is>
-          <t>5193</t>
+          <t>6220</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -12069,7 +11579,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Julia Falk</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -12080,15 +11590,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>115983394</v>
+        <v>115983616</v>
       </c>
       <c r="B104" t="n">
-        <v>78589</v>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78339</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12096,21 +11601,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>864</v>
+        <v>228579</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12120,10 +11625,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>531178</v>
+        <v>531457</v>
       </c>
       <c r="R104" t="n">
-        <v>7237757</v>
+        <v>7237480</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12150,26 +11655,26 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AR104" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5947</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -12180,7 +11685,7 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Julia Falk</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -12191,37 +11696,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>115983505</v>
+        <v>115983528</v>
       </c>
       <c r="B105" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96151</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1312</v>
+        <v>1004670</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tuffmossor</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Palustriella</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Ochyra</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12231,10 +11731,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>531002</v>
+        <v>531525</v>
       </c>
       <c r="R105" t="n">
-        <v>7237563</v>
+        <v>7237551</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -12261,12 +11761,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-09-30</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-09-30</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12280,7 +11780,7 @@
       </c>
       <c r="AR105" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>6004</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -12291,7 +11791,7 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -12302,37 +11802,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>115983525</v>
+        <v>115983521</v>
       </c>
       <c r="B106" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95765</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1312</v>
+        <v>1004672</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Källmossor</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Philonotis</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Brid.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12342,10 +11837,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>530980</v>
+        <v>531530</v>
       </c>
       <c r="R106" t="n">
-        <v>7237552</v>
+        <v>7237553</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -12372,12 +11867,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-09-30</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-09-30</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12391,7 +11886,7 @@
       </c>
       <c r="AR106" t="inlineStr">
         <is>
-          <t>5082</t>
+          <t>5977</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -12402,7 +11897,7 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -12413,37 +11908,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>115983458</v>
+        <v>115983555</v>
       </c>
       <c r="B107" t="n">
-        <v>90694</v>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95765</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1506</v>
+        <v>1004672</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Källmossor</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Philonotis</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>Brid.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12453,10 +11943,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>531634</v>
+        <v>531569</v>
       </c>
       <c r="R107" t="n">
-        <v>7237587</v>
+        <v>7237534</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -12502,7 +11992,7 @@
       </c>
       <c r="AR107" t="inlineStr">
         <is>
-          <t>6180</t>
+          <t>6099</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -12524,15 +12014,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>115983580</v>
+        <v>115983570</v>
       </c>
       <c r="B108" t="n">
-        <v>90306</v>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95765</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12540,21 +12025,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5447</v>
+        <v>1004672</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Källmossor</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Philonotis</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Brid.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12564,10 +12049,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>531462</v>
+        <v>531614</v>
       </c>
       <c r="R108" t="n">
-        <v>7237501</v>
+        <v>7237509</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12594,12 +12079,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12613,7 +12098,7 @@
       </c>
       <c r="AR108" t="inlineStr">
         <is>
-          <t>5957</t>
+          <t>6127</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -12624,1014 +12109,10 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Julia Falk</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="n">
-        <v>115983404</v>
-      </c>
-      <c r="B109" t="n">
-        <v>57680</v>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E109" t="n">
-        <v>103001</v>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Rödvingetrast</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>Turdus iliacus</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>bo, hörda ungar</t>
-        </is>
-      </c>
-      <c r="P109" t="inlineStr">
-        <is>
-          <t>Dikanäs - Kittelfjäll, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q109" t="n">
-        <v>531264</v>
-      </c>
-      <c r="R109" t="n">
-        <v>7237712</v>
-      </c>
-      <c r="S109" t="n">
-        <v>5</v>
-      </c>
-      <c r="T109" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U109" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V109" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W109" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y109" t="inlineStr">
-        <is>
-          <t>2023-06-14</t>
-        </is>
-      </c>
-      <c r="AA109" t="inlineStr">
-        <is>
-          <t>2023-06-14</t>
-        </is>
-      </c>
-      <c r="AD109" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE109" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG109" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>5250</t>
-        </is>
-      </c>
-      <c r="AT109" t="inlineStr"/>
-      <c r="AW109" t="inlineStr">
-        <is>
-          <t>Rickard Gustafsson</t>
-        </is>
-      </c>
-      <c r="AX109" t="inlineStr">
-        <is>
-          <t>Olle Kvarnbäck</t>
-        </is>
-      </c>
-      <c r="AY109" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
-        <v>115983609</v>
-      </c>
-      <c r="B110" t="n">
-        <v>78589</v>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E110" t="n">
-        <v>864</v>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Knottrig blåslav</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>Hypogymnia bitteri</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="P110" t="inlineStr">
-        <is>
-          <t>Dikanäs - Kittelfjäll, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q110" t="n">
-        <v>531493</v>
-      </c>
-      <c r="R110" t="n">
-        <v>7237482</v>
-      </c>
-      <c r="S110" t="n">
-        <v>5</v>
-      </c>
-      <c r="T110" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U110" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V110" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W110" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y110" t="inlineStr">
-        <is>
-          <t>2023-09-12</t>
-        </is>
-      </c>
-      <c r="AA110" t="inlineStr">
-        <is>
-          <t>2023-09-12</t>
-        </is>
-      </c>
-      <c r="AD110" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE110" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG110" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>5959</t>
-        </is>
-      </c>
-      <c r="AT110" t="inlineStr"/>
-      <c r="AW110" t="inlineStr">
-        <is>
-          <t>Rickard Gustafsson</t>
-        </is>
-      </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
-      </c>
-      <c r="AY110" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="n">
-        <v>115983560</v>
-      </c>
-      <c r="B111" t="n">
-        <v>77450</v>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E111" t="n">
-        <v>228579</v>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>Liten svartspik</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis nana</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="P111" t="inlineStr">
-        <is>
-          <t>Dikanäs - Kittelfjäll, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q111" t="n">
-        <v>531571</v>
-      </c>
-      <c r="R111" t="n">
-        <v>7237525</v>
-      </c>
-      <c r="S111" t="n">
-        <v>5</v>
-      </c>
-      <c r="T111" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U111" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V111" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W111" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y111" t="inlineStr">
-        <is>
-          <t>2023-09-13</t>
-        </is>
-      </c>
-      <c r="AA111" t="inlineStr">
-        <is>
-          <t>2023-09-13</t>
-        </is>
-      </c>
-      <c r="AD111" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE111" t="b">
-        <v>1</v>
-      </c>
-      <c r="AG111" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR111" t="inlineStr">
-        <is>
-          <t>6111</t>
-        </is>
-      </c>
-      <c r="AT111" t="inlineStr"/>
-      <c r="AW111" t="inlineStr">
-        <is>
-          <t>Rickard Gustafsson</t>
-        </is>
-      </c>
-      <c r="AX111" t="inlineStr">
-        <is>
-          <t>Julia Falk</t>
-        </is>
-      </c>
-      <c r="AY111" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="n">
-        <v>115983412</v>
-      </c>
-      <c r="B112" t="n">
-        <v>77463</v>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E112" t="n">
-        <v>314</v>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Vitskaftad svartspik</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis viridialba</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
-      <c r="P112" t="inlineStr">
-        <is>
-          <t>Dikanäs - Kittelfjäll, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q112" t="n">
-        <v>531217</v>
-      </c>
-      <c r="R112" t="n">
-        <v>7237675</v>
-      </c>
-      <c r="S112" t="n">
-        <v>5</v>
-      </c>
-      <c r="T112" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U112" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V112" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W112" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y112" t="inlineStr">
-        <is>
-          <t>2023-06-14</t>
-        </is>
-      </c>
-      <c r="AA112" t="inlineStr">
-        <is>
-          <t>2023-06-14</t>
-        </is>
-      </c>
-      <c r="AD112" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE112" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG112" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR112" t="inlineStr">
-        <is>
-          <t>5226</t>
-        </is>
-      </c>
-      <c r="AT112" t="inlineStr"/>
-      <c r="AW112" t="inlineStr">
-        <is>
-          <t>Rickard Gustafsson</t>
-        </is>
-      </c>
-      <c r="AX112" t="inlineStr">
-        <is>
-          <t>Robin Karlsson</t>
-        </is>
-      </c>
-      <c r="AY112" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="n">
-        <v>115983620</v>
-      </c>
-      <c r="B113" t="n">
-        <v>77463</v>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E113" t="n">
-        <v>314</v>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Vitskaftad svartspik</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis viridialba</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
-      <c r="P113" t="inlineStr">
-        <is>
-          <t>Dikanäs - Kittelfjäll, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q113" t="n">
-        <v>531455</v>
-      </c>
-      <c r="R113" t="n">
-        <v>7237478</v>
-      </c>
-      <c r="S113" t="n">
-        <v>5</v>
-      </c>
-      <c r="T113" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U113" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V113" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W113" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y113" t="inlineStr">
-        <is>
-          <t>2023-09-12</t>
-        </is>
-      </c>
-      <c r="AA113" t="inlineStr">
-        <is>
-          <t>2023-09-12</t>
-        </is>
-      </c>
-      <c r="AD113" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE113" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG113" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>5949</t>
-        </is>
-      </c>
-      <c r="AT113" t="inlineStr"/>
-      <c r="AW113" t="inlineStr">
-        <is>
-          <t>Rickard Gustafsson</t>
-        </is>
-      </c>
-      <c r="AX113" t="inlineStr">
-        <is>
-          <t>Julia Falk</t>
-        </is>
-      </c>
-      <c r="AY113" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="n">
-        <v>115983348</v>
-      </c>
-      <c r="B114" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E114" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
-      <c r="P114" t="inlineStr">
-        <is>
-          <t>Dikanäs - Kittelfjäll, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q114" t="n">
-        <v>531261</v>
-      </c>
-      <c r="R114" t="n">
-        <v>7237846</v>
-      </c>
-      <c r="S114" t="n">
-        <v>5</v>
-      </c>
-      <c r="T114" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U114" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V114" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W114" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y114" t="inlineStr">
-        <is>
-          <t>2023-06-14</t>
-        </is>
-      </c>
-      <c r="AA114" t="inlineStr">
-        <is>
-          <t>2023-06-14</t>
-        </is>
-      </c>
-      <c r="AD114" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE114" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG114" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR114" t="inlineStr">
-        <is>
-          <t>5282</t>
-        </is>
-      </c>
-      <c r="AT114" t="inlineStr"/>
-      <c r="AW114" t="inlineStr">
-        <is>
-          <t>Rickard Gustafsson</t>
-        </is>
-      </c>
-      <c r="AX114" t="inlineStr">
-        <is>
-          <t>Olle Kvarnbäck</t>
-        </is>
-      </c>
-      <c r="AY114" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="n">
-        <v>115983506</v>
-      </c>
-      <c r="B115" t="n">
-        <v>90306</v>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E115" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
-      <c r="P115" t="inlineStr">
-        <is>
-          <t>Dikanäs - Kittelfjäll, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q115" t="n">
-        <v>530949</v>
-      </c>
-      <c r="R115" t="n">
-        <v>7237563</v>
-      </c>
-      <c r="S115" t="n">
-        <v>5</v>
-      </c>
-      <c r="T115" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U115" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V115" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W115" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y115" t="inlineStr">
-        <is>
-          <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="AA115" t="inlineStr">
-        <is>
-          <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="AD115" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE115" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG115" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR115" t="inlineStr">
-        <is>
-          <t>5083</t>
-        </is>
-      </c>
-      <c r="AT115" t="inlineStr"/>
-      <c r="AW115" t="inlineStr">
-        <is>
-          <t>Rickard Gustafsson</t>
-        </is>
-      </c>
-      <c r="AX115" t="inlineStr">
-        <is>
-          <t>Olle Kvarnbäck</t>
-        </is>
-      </c>
-      <c r="AY115" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="n">
-        <v>115983517</v>
-      </c>
-      <c r="B116" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E116" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="P116" t="inlineStr">
-        <is>
-          <t>Dikanäs - Kittelfjäll, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q116" t="n">
-        <v>531031</v>
-      </c>
-      <c r="R116" t="n">
-        <v>7237555</v>
-      </c>
-      <c r="S116" t="n">
-        <v>5</v>
-      </c>
-      <c r="T116" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U116" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V116" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W116" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y116" t="inlineStr">
-        <is>
-          <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="AA116" t="inlineStr">
-        <is>
-          <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="AD116" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE116" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG116" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>5148</t>
-        </is>
-      </c>
-      <c r="AT116" t="inlineStr"/>
-      <c r="AW116" t="inlineStr">
-        <is>
-          <t>Rickard Gustafsson</t>
-        </is>
-      </c>
-      <c r="AX116" t="inlineStr">
-        <is>
-          <t>Olle Kvarnbäck</t>
-        </is>
-      </c>
-      <c r="AY116" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="n">
-        <v>115983335</v>
-      </c>
-      <c r="B117" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E117" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="P117" t="inlineStr">
-        <is>
-          <t>Dikanäs - Kittelfjäll, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q117" t="n">
-        <v>531223</v>
-      </c>
-      <c r="R117" t="n">
-        <v>7237901</v>
-      </c>
-      <c r="S117" t="n">
-        <v>5</v>
-      </c>
-      <c r="T117" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U117" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V117" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W117" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y117" t="inlineStr">
-        <is>
-          <t>2023-06-14</t>
-        </is>
-      </c>
-      <c r="AA117" t="inlineStr">
-        <is>
-          <t>2023-06-14</t>
-        </is>
-      </c>
-      <c r="AD117" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE117" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG117" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>5280</t>
-        </is>
-      </c>
-      <c r="AT117" t="inlineStr"/>
-      <c r="AW117" t="inlineStr">
-        <is>
-          <t>Rickard Gustafsson</t>
-        </is>
-      </c>
-      <c r="AX117" t="inlineStr">
-        <is>
-          <t>Robin Karlsson</t>
-        </is>
-      </c>
-      <c r="AY117" t="inlineStr">
         <is>
           <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
         </is>
